--- a/artfynd/A 26579-2022 artfynd.xlsx
+++ b/artfynd/A 26579-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130449402</v>
       </c>
       <c r="B2" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130449397</v>
       </c>
       <c r="B3" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130449401</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130449391</v>
       </c>
       <c r="B6" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>130449395</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>130449398</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>130449399</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26579-2022 artfynd.xlsx
+++ b/artfynd/A 26579-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130449402</v>
+        <v>130449397</v>
       </c>
       <c r="B2" t="n">
-        <v>79259</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>769699</v>
+        <v>769654</v>
       </c>
       <c r="R2" t="n">
         <v>7289245</v>
@@ -766,6 +766,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130449397</v>
+        <v>130449398</v>
       </c>
       <c r="B3" t="n">
-        <v>83081</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>769654</v>
+        <v>769655</v>
       </c>
       <c r="R3" t="n">
-        <v>7289245</v>
+        <v>7289244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,11 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130449392</v>
+        <v>130449401</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hötjärnmyran, Husavan, Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>769671</v>
+        <v>769633</v>
       </c>
       <c r="R4" t="n">
-        <v>7289231</v>
+        <v>7289237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,11 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>död björk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130449401</v>
+        <v>130449391</v>
       </c>
       <c r="B5" t="n">
-        <v>79235</v>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769633</v>
+        <v>769686</v>
       </c>
       <c r="R5" t="n">
-        <v>7289237</v>
+        <v>7289228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130449391</v>
+        <v>130449402</v>
       </c>
       <c r="B6" t="n">
-        <v>79259</v>
+        <v>79351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769686</v>
+        <v>769699</v>
       </c>
       <c r="R6" t="n">
-        <v>7289228</v>
+        <v>7289245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130449395</v>
+        <v>130449404</v>
       </c>
       <c r="B7" t="n">
-        <v>80244</v>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769661</v>
+        <v>769831</v>
       </c>
       <c r="R7" t="n">
-        <v>7289236</v>
+        <v>7289214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1306,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1337,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130449394</v>
+        <v>130449395</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,39 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hötjärnmyran, Husavan, Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769667</v>
+        <v>769661</v>
       </c>
       <c r="R8" t="n">
-        <v>7289231</v>
+        <v>7289236</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1416,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>död björk</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1454,32 +1434,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130449398</v>
+        <v>130449399</v>
       </c>
       <c r="B9" t="n">
-        <v>79235</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769655</v>
+        <v>769649</v>
       </c>
       <c r="R9" t="n">
-        <v>7289244</v>
+        <v>7289240</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,6 +1525,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1561,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130449399</v>
+        <v>130449393</v>
       </c>
       <c r="B10" t="n">
-        <v>80244</v>
+        <v>4819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100857</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Strand, 1938</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hötjärnmyran, Husavan, Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769649</v>
+        <v>769665</v>
       </c>
       <c r="R10" t="n">
-        <v>7289240</v>
+        <v>7289228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1645,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>död björk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130449393</v>
+        <v>130449392</v>
       </c>
       <c r="B11" t="n">
-        <v>4817</v>
+        <v>8444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100857</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Robust tickgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dorcatoma robusta</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Strand, 1938</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769665</v>
+        <v>769671</v>
       </c>
       <c r="R11" t="n">
-        <v>7289228</v>
+        <v>7289231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,6 +1777,235 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130449394</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hötjärnmyran, Husavan, Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>769667</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7289231</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130449400</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hötjärnmyran, Husavan, Arvidsträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>769646</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7289235</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26579-2022 artfynd.xlsx
+++ b/artfynd/A 26579-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449397</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449391</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449402</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449395</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449399</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449393</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449392</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449394</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,8 +2066,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130449400</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>